--- a/sources/julia_step8.xlsx
+++ b/sources/julia_step8.xlsx
@@ -1057,6 +1057,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>1b569aeb-dd63-4db9-bfe2-caa3a868a11d</t>
+        </is>
+      </c>
       <c r="Z9" t="inlineStr">
         <is>
           <t>1b569aeb-dd63-4db9-bfe2-caa3a868a11d</t>
@@ -1119,6 +1124,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>48718773-f00b-471d-8dc4-830794a42ebc</t>
+        </is>
+      </c>
       <c r="Z10" t="inlineStr">
         <is>
           <t>48718773-f00b-471d-8dc4-830794a42ebc</t>
@@ -1181,6 +1191,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>35dc67c0-d4fa-495c-aefc-39f34e65507b</t>
+        </is>
+      </c>
       <c r="Z11" t="inlineStr">
         <is>
           <t>35dc67c0-d4fa-495c-aefc-39f34e65507b</t>
@@ -1241,6 +1256,11 @@
       <c r="U12" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>b70b8f8a-633b-40a2-8811-5f4191813631</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -9321,6 +9341,11 @@
           <t>hmmhLmhhLm</t>
         </is>
       </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>f26af970-57e3-45d4-baba-6711c2809508</t>
+        </is>
+      </c>
       <c r="Z103" t="inlineStr">
         <is>
           <t>f26af970-57e3-45d4-baba-6711c2809508</t>
@@ -9368,6 +9393,11 @@
           <t>hmmhLmmLm!</t>
         </is>
       </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>8ba99c8f-7b6d-46d5-860f-492405778df4</t>
+        </is>
+      </c>
       <c r="Z104" t="inlineStr">
         <is>
           <t>8ba99c8f-7b6d-46d5-860f-492405778df4</t>
@@ -9413,6 +9443,11 @@
       <c r="S105" t="inlineStr">
         <is>
           <t>hmmhLmmmLm</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>12d35c24-0209-43bc-a4fa-a6173fd493c0</t>
         </is>
       </c>
       <c r="Z105" t="inlineStr">

--- a/sources/julia_step8.xlsx
+++ b/sources/julia_step8.xlsx
@@ -417,37 +417,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB105"/>
+  <dimension ref="A1:AC105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col hidden="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col hidden="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col hidden="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
-    <col hidden="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col hidden="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col hidden="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col hidden="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col hidden="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col hidden="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col hidden="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
-    <col hidden="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
-    <col hidden="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="124" customWidth="1" min="23" max="23"/>
-    <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="38" customWidth="1" min="25" max="25"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col hidden="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col hidden="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="124" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
     <col width="38" customWidth="1" min="26" max="26"/>
     <col width="38" customWidth="1" min="27" max="27"/>
-    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="38" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -475,125 +476,130 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="R2" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R2" s="1" t="inlineStr">
+      <c r="S2" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S2" s="1" t="inlineStr">
+      <c r="T2" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T2" s="1" t="inlineStr">
+      <c r="U2" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U2" s="1" t="inlineStr">
+      <c r="V2" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V2" s="1" t="inlineStr">
+      <c r="W2" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W2" s="1" t="inlineStr">
+      <c r="X2" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X2" s="1" t="inlineStr">
+      <c r="Y2" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="Z2" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="AA2" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AB2" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB2" s="1" t="inlineStr">
+      <c r="AC2" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -610,57 +616,57 @@
           <t>1+3</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Death Valley Bomb</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Death Valley Bomb</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>ab6d9b06-f5f7-4feb-9f49-383448e4e096</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>82e2360f-3cd0-425d-af5a-c5d8e5e52627</t>
         </is>
@@ -677,57 +683,57 @@
           <t>2+4</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Fisherman Suplex</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Fisherman Suplex</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>ed821a05-2ec4-494a-a83b-a9d19455605a</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>d29502bb-765d-44e2-8876-21234ac961c4</t>
         </is>
@@ -744,57 +750,57 @@
           <t>df+1+2</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Arm Lock Suplex</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Arm Lock Suplex</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>1+2</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0ecb3935-db08-456b-9028-a384f068cad7</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>bd4883ff-ba97-43f1-8b7a-e75e4b235bd4</t>
         </is>
@@ -811,57 +817,57 @@
           <t>d,DB+1+3</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Waist Suplex</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Waist Suplex</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>8c936c68-0894-4e5c-a2be-40ff8f18293a</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>6fcd28c4-ed8d-4248-a970-04c30fdf4c0c</t>
         </is>
@@ -878,57 +884,57 @@
           <t>FC+db,d,db+1+2</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Cross Arm Lock</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Cross Arm Lock</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>1+2</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>e6a34a80-1f3d-4591-abd0-e675e4465a13</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>1beb1ed8-ad26-4266-b8e8-0b6b1905d4fd</t>
         </is>
@@ -945,57 +951,57 @@
           <t>qcb,f+2</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Mad Axes</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Mad Axes</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>14,14,14</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>14,14,14</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>1+2</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>e276813a-1ee1-4285-afb3-2cc48b9ea3f7</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>abc48219-3324-45bc-b4e5-eba12deb6d7b</t>
         </is>
@@ -1012,62 +1018,62 @@
           <t>b+2</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Arm Whip</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Arm Whip</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>d</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>Special Tag Throw with Michelle only. Michelle finishes with a Lariat. Total damage is 12,24.</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>1b569aeb-dd63-4db9-bfe2-caa3a868a11d</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>1b569aeb-dd63-4db9-bfe2-caa3a868a11d</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1091,50 +1097,55 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>Running Bulldog</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Running Bulldog</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>48718773-f00b-471d-8dc4-830794a42ebc</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>48718773-f00b-471d-8dc4-830794a42ebc</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1158,50 +1169,55 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>Twisted Sister</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Twisted Sister</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>35dc67c0-d4fa-495c-aefc-39f34e65507b</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>35dc67c0-d4fa-495c-aefc-39f34e65507b</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1225,50 +1241,55 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>Spinning Air Neckbreaker</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Spinning Air Neckbreaker</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Back</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>b70b8f8a-633b-40a2-8811-5f4191813631</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>b70b8f8a-633b-40a2-8811-5f4191813631</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1300,125 +1321,130 @@
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E15" s="1" t="inlineStr">
+      <c r="F15" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F15" s="1" t="inlineStr">
+      <c r="G15" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G15" s="1" t="inlineStr">
+      <c r="H15" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H15" s="1" t="inlineStr">
+      <c r="I15" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I15" s="1" t="inlineStr">
+      <c r="J15" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J15" s="1" t="inlineStr">
+      <c r="K15" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K15" s="1" t="inlineStr">
+      <c r="L15" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L15" s="1" t="inlineStr">
+      <c r="M15" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M15" s="1" t="inlineStr">
+      <c r="N15" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N15" s="1" t="inlineStr">
+      <c r="O15" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O15" s="1" t="inlineStr">
+      <c r="P15" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P15" s="1" t="inlineStr">
+      <c r="Q15" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q15" s="1" t="inlineStr">
+      <c r="R15" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R15" s="1" t="inlineStr">
+      <c r="S15" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S15" s="1" t="inlineStr">
+      <c r="T15" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T15" s="1" t="inlineStr">
+      <c r="U15" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U15" s="1" t="inlineStr">
+      <c r="V15" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V15" s="1" t="inlineStr">
+      <c r="W15" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W15" s="1" t="inlineStr">
+      <c r="X15" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X15" s="1" t="inlineStr">
+      <c r="Y15" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y15" s="1" t="inlineStr">
+      <c r="Z15" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z15" s="1" t="inlineStr">
+      <c r="AA15" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA15" s="1" t="inlineStr">
+      <c r="AB15" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB15" s="1" t="inlineStr">
+      <c r="AC15" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -1435,77 +1461,77 @@
           <t>1</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>15035c38-d5a6-49f9-bea8-f587a7392e1a</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>624135a9-7295-48fa-ba6c-31a86bc446c3</t>
         </is>
@@ -1522,77 +1548,77 @@
           <t>2</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>8e21dae9-4968-476e-b16c-22b5b747ee5e</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>4e8f95f2-3777-4134-9089-cbf3b2fe7533</t>
         </is>
@@ -1609,77 +1635,77 @@
           <t>3</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>6e6b42cc-fe86-458b-9922-127dc30031c0</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>2ee732ff-25d9-46a8-8c45-e56593085910</t>
         </is>
@@ -1696,77 +1722,77 @@
           <t>4</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>cca5e538-aae6-400e-a730-3420008d1646</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>6f72c047-a692-4df5-a606-8eafb518215d</t>
         </is>
@@ -1783,77 +1809,77 @@
           <t>f+1</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>a6a7b0f8-e04c-46c8-bd17-e2f073028d01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>45938629-f4a5-4400-9d57-551381ccaddd</t>
         </is>
@@ -1870,77 +1896,77 @@
           <t>f+2</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>1af6facc-f33e-491c-8dce-850506bd0cf8</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>7a6f27d8-bf4f-4e57-8fc6-2c7353a60dba</t>
         </is>
@@ -1957,77 +1983,77 @@
           <t>f+3</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>78a06659-d397-4743-bd01-9a9482d267b3</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>05488562-ac28-47a2-9d89-19c17aab4ef3</t>
         </is>
@@ -2044,77 +2070,77 @@
           <t>f+4</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>e4927ca5-bc4d-460d-adae-c61141dbfdcb</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>8795513e-8417-4e86-b8ba-a6a98274ff37</t>
         </is>
@@ -2131,77 +2157,77 @@
           <t>d+1</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>e22b57f5-5424-4c98-a000-6bb30da58f45</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>f4bd9baf-693c-4965-9b51-209ffe480dec</t>
         </is>
@@ -2218,77 +2244,77 @@
           <t>d+2</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>646872c0-d619-4bbc-b72f-00e9b79ef036</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>c380c889-63ec-46ed-b1e8-16139acf8b7d</t>
         </is>
@@ -2305,77 +2331,77 @@
           <t>d+3</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>2897ab35-7c69-4caf-8eaa-9ff9f8372fe1</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>7db50050-6a19-4e76-85b6-2b01cc4350eb</t>
         </is>
@@ -2392,77 +2418,77 @@
           <t>d+4</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>4b126cb7-06af-4478-856c-bc3c55d1e6e1</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>9559c6a0-e111-4c90-98a8-17922e344950</t>
         </is>
@@ -2479,77 +2505,77 @@
           <t>FC+1</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>0dacef04-e59d-419d-81f2-aeb369ac7ff0</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>52254c0f-0579-4e8b-bb82-9bf23b82c059</t>
         </is>
@@ -2566,77 +2592,77 @@
           <t>FC+2</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>722d6e66-1274-44d2-ad76-2c4724acf79c</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>5d9e08dc-586c-42e0-b05d-d53e0722c953</t>
         </is>
@@ -2653,77 +2679,77 @@
           <t>FC+3</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>0b5550a4-0c1a-4674-ba2e-3a1456aa5577</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>13c153c4-7ad5-483e-8a55-9ca62e530507</t>
         </is>
@@ -2740,77 +2766,77 @@
           <t>FC+4</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>f486bcc7-f067-4a17-b512-ff2d8292f640</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>bf0d7423-b624-466a-847b-1c1c6c3e527d</t>
         </is>
@@ -2827,77 +2853,77 @@
           <t>WS+1</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>515dca44-c4b4-4aac-8a57-a5bd63dca6a7</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>78a7a936-3e93-40d8-8cee-62959e8cf78a</t>
         </is>
@@ -2914,77 +2940,77 @@
           <t>WS+2</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>0e2c078f-d1de-4d37-9205-f427cbbe022f</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>54235914-59eb-4a20-b36d-91c541cc2e94</t>
         </is>
@@ -3001,77 +3027,77 @@
           <t>WS+3</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>4d3a0917-e813-4c55-9da5-3e9775c5241a</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>778d503d-7812-4de4-b0ef-96a4b78ba20c</t>
         </is>
@@ -3088,77 +3114,77 @@
           <t>WS+4</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>fcb15e85-d11e-41bb-b153-1f50e75b8ba0</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>2729435e-e9ba-439c-b813-74909c92bb10</t>
         </is>
@@ -3175,77 +3201,77 @@
           <t>df+1</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>81941edd-8313-4c5d-808a-69e5391f1646</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>2ab0708d-e9f2-4cfe-9bfe-4182938cf9c5</t>
         </is>
@@ -3262,77 +3288,77 @@
           <t>df+2</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>5de20d7c-6e9f-4b4d-b3be-6f3019ed23d4</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>a8b16b5c-ff44-4b9e-943a-590946b12392</t>
         </is>
@@ -3349,77 +3375,77 @@
           <t>df+3</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="R38" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y38" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>8de3341e-a280-448e-be3c-8871c83bdc2a</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
+      <c r="AA38" t="inlineStr">
         <is>
           <t>84a1032e-e3f1-493f-91f8-0a7635613eca</t>
         </is>
@@ -3436,77 +3462,77 @@
           <t>df+4</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="R39" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>565e0ea5-fec4-40e7-b756-fceb99f74fe3</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>53380c85-00db-4d12-b976-2b7a7ae68c2a</t>
         </is>
@@ -3538,125 +3564,130 @@
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E42" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E42" s="1" t="inlineStr">
+      <c r="F42" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F42" s="1" t="inlineStr">
+      <c r="G42" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G42" s="1" t="inlineStr">
+      <c r="H42" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H42" s="1" t="inlineStr">
+      <c r="I42" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I42" s="1" t="inlineStr">
+      <c r="J42" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J42" s="1" t="inlineStr">
+      <c r="K42" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K42" s="1" t="inlineStr">
+      <c r="L42" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L42" s="1" t="inlineStr">
+      <c r="M42" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M42" s="1" t="inlineStr">
+      <c r="N42" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N42" s="1" t="inlineStr">
+      <c r="O42" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O42" s="1" t="inlineStr">
+      <c r="P42" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P42" s="1" t="inlineStr">
+      <c r="Q42" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q42" s="1" t="inlineStr">
+      <c r="R42" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R42" s="1" t="inlineStr">
+      <c r="S42" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S42" s="1" t="inlineStr">
+      <c r="T42" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T42" s="1" t="inlineStr">
+      <c r="U42" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U42" s="1" t="inlineStr">
+      <c r="V42" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V42" s="1" t="inlineStr">
+      <c r="W42" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W42" s="1" t="inlineStr">
+      <c r="X42" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X42" s="1" t="inlineStr">
+      <c r="Y42" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y42" s="1" t="inlineStr">
+      <c r="Z42" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z42" s="1" t="inlineStr">
+      <c r="AA42" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA42" s="1" t="inlineStr">
+      <c r="AB42" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB42" s="1" t="inlineStr">
+      <c r="AC42" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -3673,92 +3704,92 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Twin Arrow</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Twin Arrow</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="W43" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>4d1a49f3-ed23-4e20-b00e-1ec062066e8e</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
+      <c r="AA43" t="inlineStr">
         <is>
           <t>7dc4a2ca-d636-412a-984b-af70d0bc70b4</t>
         </is>
@@ -3775,97 +3806,97 @@
           <t>f+1</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Flash Uppercut</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Flash Uppercut</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="W44" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="Y44" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>e1224874-813b-4cb5-8863-09a0aa463239</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
+      <c r="AA44" t="inlineStr">
         <is>
           <t>20ae85e2-a635-4efe-aa12-c4d7da2120df</t>
         </is>
@@ -3889,85 +3920,90 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>WR+1</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>Flash Punch</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Flash Punch</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>2f02cadd-691c-4878-8cc0-ed165628df8d</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
+      <c r="AA45" t="inlineStr">
         <is>
           <t>25ce8b7e-9f3a-435f-92d1-f350d26aecc0</t>
         </is>
@@ -3984,92 +4020,92 @@
           <t>d,df+1&lt;2</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>– Flash Elbow</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Flash Punch – Flash Elbow</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>-8 -7</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>-2 KD</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>+3 KD</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>14,21</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>FSc</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>90835ff4-9095-4137-8242-a717dbeaeab8</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
+      <c r="AA46" t="inlineStr">
         <is>
           <t>bbd933e6-0ed1-45ae-83ba-d1b80a2aca2b</t>
         </is>
       </c>
-      <c r="AA46" t="inlineStr">
+      <c r="AB46" t="inlineStr">
         <is>
           <t>2f02cadd-691c-4878-8cc0-ed165628df8d</t>
         </is>
@@ -4086,87 +4122,87 @@
           <t>1~1</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>G-Clef - Club Fist</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>G-Clef - Club Fist</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>0 -15</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>0 -15</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>+6 -4</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>+6 -4</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>+6 -4</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>+6 -4</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>10,5</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>10,5</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>hm</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>hm</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t>f133d0b0-0e08-4804-a099-7e4bd0e986b5</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
+      <c r="AA47" t="inlineStr">
         <is>
           <t>f5055146-693c-4610-927e-1c1ecc7ffd50</t>
         </is>
@@ -4183,97 +4219,97 @@
           <t>1~1,1</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>– Flash Uppercut</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>G-Clef - Club Fist – Flash Uppercut</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>0 -15 -14</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>+6 -4 KD</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>+6 -4 KD</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>10,5,21</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>hmm</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="Y48" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y48" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t>6fff6863-e889-458b-aa91-4b5cc27f07cb</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
+      <c r="AA48" t="inlineStr">
         <is>
           <t>8db566fb-78d9-4496-b899-aaa34dbac5dc</t>
         </is>
       </c>
-      <c r="AA48" t="inlineStr">
+      <c r="AB48" t="inlineStr">
         <is>
           <t>f133d0b0-0e08-4804-a099-7e4bd0e986b5</t>
         </is>
@@ -4290,87 +4326,87 @@
           <t>1~1,4,3</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>– Bow - Arrow</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>G-Clef - Club Fist – Bow - Arrow</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>-13 -12</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>0 -15 -13 -12</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>-2 KD</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>+6 -4 -2 KD</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>-2 KD</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>+6 -4 -2 KD</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>12,15</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>10,5,12,15</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>Lm</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>hmLm</t>
         </is>
       </c>
-      <c r="Y49" t="inlineStr">
+      <c r="Z49" t="inlineStr">
         <is>
           <t>697b57ac-f4e1-4b88-af3c-1c93b7f5ef92</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
+      <c r="AA49" t="inlineStr">
         <is>
           <t>cafc3c93-4416-4260-b77c-c2bcb2b34bd1</t>
         </is>
       </c>
-      <c r="AA49" t="inlineStr">
+      <c r="AB49" t="inlineStr">
         <is>
           <t>f133d0b0-0e08-4804-a099-7e4bd0e986b5</t>
         </is>
@@ -4387,87 +4423,87 @@
           <t>df+1</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Club Fist</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Club Fist</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
+      <c r="Z50" t="inlineStr">
         <is>
           <t>cdda1d7c-4cfd-4571-93ca-ca2fd57ed026</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
+      <c r="AA50" t="inlineStr">
         <is>
           <t>20d68298-0458-4971-ad79-3bdb2c6bc45d</t>
         </is>
@@ -4484,97 +4520,97 @@
           <t>df+1,1</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>– Flash Uppercut</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Club Fist – Flash Uppercut</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>-15 -14</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>-4 KD</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>-4 KD</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>8,21</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
+      <c r="W51" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="Y51" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y51" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>efdd89f1-e74a-4052-a24f-85b56505262f</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
+      <c r="AA51" t="inlineStr">
         <is>
           <t>3fc32248-c49c-4918-a460-249b714182e7</t>
         </is>
       </c>
-      <c r="AA51" t="inlineStr">
+      <c r="AB51" t="inlineStr">
         <is>
           <t>cdda1d7c-4cfd-4571-93ca-ca2fd57ed026</t>
         </is>
@@ -4591,87 +4627,87 @@
           <t>df+1,4,3</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>– Bow - Arrow</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Club Fist – Bow - Arrow</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>-13 -12</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>-15 -13 -12</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>-2 KD</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>-4 -2 KD</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>-2 KD</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>-4 -2 KD</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>12,15</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="R52" t="inlineStr">
         <is>
           <t>8,12,15</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>Lm</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>mLm</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>15cd3b1a-c236-4443-abd8-0bb0c83297ea</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
+      <c r="AA52" t="inlineStr">
         <is>
           <t>2e64b986-2f72-4b15-a081-83a778c18d06</t>
         </is>
       </c>
-      <c r="AA52" t="inlineStr">
+      <c r="AB52" t="inlineStr">
         <is>
           <t>cdda1d7c-4cfd-4571-93ca-ca2fd57ed026</t>
         </is>
@@ -4688,92 +4724,92 @@
           <t>1~2</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>G-Clef - Gut Punch</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>G-Clef - Gut Punch</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>0 -15</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>0 -15</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>+6 +5</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>+6 +5</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>+6 +5</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>+6 +5</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>10,8</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="R53" t="inlineStr">
         <is>
           <t>10,8</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>hm</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>hm</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>If the 1st hit is a counter hit, the damage of the 2nd hit will be 10. If the string is complete (1~2~1) the damage is 15.</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>2b4933ca-1985-4996-9512-57f643232731</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
+      <c r="AA53" t="inlineStr">
         <is>
           <t>5b055c92-7199-46d7-9a66-b81f058cf33f</t>
         </is>
@@ -4790,87 +4826,87 @@
           <t>1~2~1</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>– Skyscraper Cannon</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>G-Clef - Gut Punch – Skyscraper Cannon</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>0 -15</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>+6 +5</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>+6 +5</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="R54" t="inlineStr">
         <is>
           <t>10,8,21</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>hmm</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr">
+      <c r="W54" t="inlineStr">
         <is>
           <t>CH</t>
         </is>
       </c>
-      <c r="W54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>The 3rd only occurs if the 1st hit was a counter hit or the 2nd hit connected on the opponents side.</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
+      <c r="Y54" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>6275a354-d231-4442-8af8-0fc378c274f5</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
+      <c r="AA54" t="inlineStr">
         <is>
           <t>df19be7c-d1b5-4569-ad72-d09202c8ce24</t>
         </is>
       </c>
-      <c r="AA54" t="inlineStr">
+      <c r="AB54" t="inlineStr">
         <is>
           <t>2b4933ca-1985-4996-9512-57f643232731</t>
         </is>
@@ -4887,92 +4923,92 @@
           <t>1~2,3</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>– Low Kick</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>G-Clef - Gut Punch – Low Kick</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>0 -15 -17</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>+6 +5 -3</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>+6 +5 -3</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>10,8,10</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>hmL</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr">
+      <c r="W55" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t>bf4d512c-5f0b-46cc-b1ce-d720fde5db97</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
+      <c r="AA55" t="inlineStr">
         <is>
           <t>f86a95d0-6e88-4df9-b0d9-eac609a7dcd1</t>
         </is>
       </c>
-      <c r="AA55" t="inlineStr">
+      <c r="AB55" t="inlineStr">
         <is>
           <t>2b4933ca-1985-4996-9512-57f643232731</t>
         </is>
@@ -4989,87 +5025,87 @@
           <t>1~2,4</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>– High Kick</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>G-Clef - Gut Punch – High Kick</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>0 -15 -7</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>+6 +5 -7</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>+6 +5 KD</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="R56" t="inlineStr">
         <is>
           <t>10,8,20</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>hmh</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>23597e7c-315f-44cb-bc68-f45b05b788b8</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
+      <c r="AA56" t="inlineStr">
         <is>
           <t>84d6f14f-4c06-4a11-833c-89e4d77303cc</t>
         </is>
       </c>
-      <c r="AA56" t="inlineStr">
+      <c r="AB56" t="inlineStr">
         <is>
           <t>2b4933ca-1985-4996-9512-57f643232731</t>
         </is>
@@ -5086,87 +5122,87 @@
           <t>f,f+1</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>Party Crasher</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>Party Crasher</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="R57" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
         <is>
           <t>2fcdf90d-a1c6-4635-b48c-efa347b4bf34</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
+      <c r="AA57" t="inlineStr">
         <is>
           <t>eed8a7cc-f9f5-4db5-9a8e-13154acd5f2e</t>
         </is>
@@ -5183,92 +5219,92 @@
           <t>f,f+1&lt;4</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>– Skyscraper Kick</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>Party Crasher – Skyscraper Kick</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>-2 -11</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="R58" t="inlineStr">
         <is>
           <t>10,15</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr">
+      <c r="W58" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr">
+      <c r="Z58" t="inlineStr">
         <is>
           <t>a0d438e2-6a92-4d84-95e7-ae9c82e1971a</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
+      <c r="AA58" t="inlineStr">
         <is>
           <t>06fcb74c-7ef1-4910-baa5-5ff549d169f1</t>
         </is>
       </c>
-      <c r="AA58" t="inlineStr">
+      <c r="AB58" t="inlineStr">
         <is>
           <t>2fcdf90d-a1c6-4635-b48c-efa347b4bf34</t>
         </is>
@@ -5285,92 +5321,92 @@
           <t>f+1~2</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>Palm Explosion</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Palm Explosion</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="R59" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
+      <c r="W59" t="inlineStr">
         <is>
           <t>FSc</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr">
+      <c r="Z59" t="inlineStr">
         <is>
           <t>a4c9455c-b3f7-445f-bb03-bc9714978245</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
+      <c r="AA59" t="inlineStr">
         <is>
           <t>6ea6a131-4528-47b9-b547-5ca7fbc36c49</t>
         </is>
@@ -5387,102 +5423,102 @@
           <t>f+1+2</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>Shove It Up</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>Shove It Up</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="R60" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr">
+      <c r="W60" t="inlineStr">
         <is>
           <t>JGc</t>
         </is>
       </c>
-      <c r="W60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>The uppercut does not need to be a counter hit to buffer a tag..</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
+      <c r="Y60" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y60" t="inlineStr">
+      <c r="Z60" t="inlineStr">
         <is>
           <t>1242cb0e-50bb-40b6-b2a1-ca87df3c4f00</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
+      <c r="AA60" t="inlineStr">
         <is>
           <t>f8303771-3790-4f2d-b82e-a3dd4030c9ac</t>
         </is>
@@ -5499,87 +5535,87 @@
           <t>1+4,3</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>Club Fist - Bow - Arrow</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Club Fist - Bow - Arrow</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>20 x x</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>20 x x</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>x -13 12</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>x -13 12</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>x -2 KD</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>x -2 KD</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>x -2 KD</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>x -2 KD</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>12,12,15</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="R61" t="inlineStr">
         <is>
           <t>12,12,15</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>mLm</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>mLm</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr">
+      <c r="Z61" t="inlineStr">
         <is>
           <t>ecf9ec9c-b22c-4f6a-9f5c-8f0b3d51b517</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
+      <c r="AA61" t="inlineStr">
         <is>
           <t>32c39285-0d95-467e-b604-b48881824316</t>
         </is>
@@ -5596,87 +5632,87 @@
           <t>df+2</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>Gut Punch</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>Gut Punch</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="R62" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="T62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>0352fade-12a8-40f1-8a4c-f0193680f01a</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
+      <c r="AA62" t="inlineStr">
         <is>
           <t>3a9d5340-469a-44ee-bdf1-f63ac00ab3e1</t>
         </is>
@@ -5693,87 +5729,87 @@
           <t>df+2,1</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>– Skyscraper Cannon</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>Gut Punch – Skyscraper Cannon</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="R63" t="inlineStr">
         <is>
           <t>10,21</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="T63" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="V63" t="inlineStr">
+      <c r="W63" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="W63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>In the d/f+2,1 string the damage of the d/f+2 is 15. And has to hit from the front to work.</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="Y63" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y63" t="inlineStr">
+      <c r="Z63" t="inlineStr">
         <is>
           <t>c672c34b-05e9-4636-968c-72c907a897d8</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
+      <c r="AA63" t="inlineStr">
         <is>
           <t>6d1dada0-2ef7-4f8e-a7b1-3573f3ef791b</t>
         </is>
       </c>
-      <c r="AA63" t="inlineStr">
+      <c r="AB63" t="inlineStr">
         <is>
           <t>0352fade-12a8-40f1-8a4c-f0193680f01a</t>
         </is>
@@ -5790,92 +5826,92 @@
           <t>df+2,3</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>– Low Kick</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Gut Punch – Low Kick</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>-6 -17</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>+5 -3</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>+5 -3</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="R64" t="inlineStr">
         <is>
           <t>10,10</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="T64" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="V64" t="inlineStr">
+      <c r="W64" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Y64" t="inlineStr">
+      <c r="Z64" t="inlineStr">
         <is>
           <t>bbe27077-b04b-4ce7-8f7b-350b6a915118</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
+      <c r="AA64" t="inlineStr">
         <is>
           <t>5217e99c-00b5-4542-9d8e-06462325f261</t>
         </is>
       </c>
-      <c r="AA64" t="inlineStr">
+      <c r="AB64" t="inlineStr">
         <is>
           <t>0352fade-12a8-40f1-8a4c-f0193680f01a</t>
         </is>
@@ -5892,87 +5928,87 @@
           <t>df+2,4</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>– High Kick</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>Gut Punch – High Kick</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>-6 -7</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>+5 -7</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>+5 KD</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="R65" t="inlineStr">
         <is>
           <t>10,20</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="T65" t="inlineStr">
         <is>
           <t>mh</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t>71e7fef9-4e10-447a-b667-59a4aa8fc853</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
+      <c r="AA65" t="inlineStr">
         <is>
           <t>873ceac2-385c-469e-87f0-b0e08e69ba50</t>
         </is>
       </c>
-      <c r="AA65" t="inlineStr">
+      <c r="AB65" t="inlineStr">
         <is>
           <t>0352fade-12a8-40f1-8a4c-f0193680f01a</t>
         </is>
@@ -5996,95 +6032,100 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t>2+3,1</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
           <t>Ultimate Cannon</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>Ultimate Cannon</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>10 x x</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>10 x x</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>x -11 -8</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>x -11 -8</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>x 0 KD</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>x 0 KD</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>x 0 KD</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>x 0 KD</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>10_8,9,25</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>142</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="R66" t="inlineStr">
         <is>
           <t>10_8,9,25</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr">
+      <c r="S66" t="inlineStr">
         <is>
           <t>smm</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="T66" t="inlineStr">
         <is>
           <t>smm</t>
         </is>
       </c>
-      <c r="V66" t="inlineStr">
+      <c r="W66" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
+      <c r="Y66" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y66" t="inlineStr">
+      <c r="Z66" t="inlineStr">
         <is>
           <t>93a991d8-f45d-458b-ae7c-eef2802ad600</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
+      <c r="AA66" t="inlineStr">
         <is>
           <t>6718fa05-f529-4234-83f2-ea0ff0e53f80</t>
         </is>
@@ -6108,90 +6149,95 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t>FC+df+2</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>Flash Elbow</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Flash Elbow</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>-20</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>-20</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
+      <c r="P67" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="R67" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="T67" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr">
+      <c r="W67" t="inlineStr">
         <is>
           <t>FSc</t>
         </is>
       </c>
-      <c r="Y67" t="inlineStr">
+      <c r="Z67" t="inlineStr">
         <is>
           <t>68426f4f-f3e0-4291-97a7-3a7bd296591b</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
+      <c r="AA67" t="inlineStr">
         <is>
           <t>0576cf8f-0403-4eb2-9a84-e6f6aac6ce18</t>
         </is>
@@ -6208,92 +6254,92 @@
           <t>SS+2</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>Parting Fist</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Parting Fist</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="R68" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="T68" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V68" t="inlineStr">
+      <c r="W68" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="Y68" t="inlineStr">
+      <c r="Z68" t="inlineStr">
         <is>
           <t>33acabf7-da8d-4bc4-abdf-3b266034d3f3</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
+      <c r="AA68" t="inlineStr">
         <is>
           <t>e29b369c-42e6-465f-a9d8-c71332c19eb2</t>
         </is>
@@ -6317,95 +6363,100 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t>2~b</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
           <t>Arm Whip</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>Arm Whip</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
+      <c r="P69" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr">
+      <c r="R69" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="T69" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="V69" t="inlineStr">
+      <c r="W69" t="inlineStr">
         <is>
           <t>OB</t>
         </is>
       </c>
-      <c r="W69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>The Arm Whip needs to hit for Julia to spin around the opponent.</t>
         </is>
       </c>
-      <c r="Y69" t="inlineStr">
+      <c r="Z69" t="inlineStr">
         <is>
           <t>a72aa904-1124-409f-a75b-cb6b7a95fa1f</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
+      <c r="AA69" t="inlineStr">
         <is>
           <t>3eaddb93-856e-4286-9afe-2a136672f1c6</t>
         </is>
@@ -6422,92 +6473,102 @@
           <t>b+2,1+2</t>
         </is>
       </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t>b+2,5</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
           <t>– Back Push</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>Arm Whip – Back Push</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>0 +2</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>-1 +2</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>-1 +2</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="R70" t="inlineStr">
         <is>
           <t>12,-</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
+      <c r="S70" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="T70" t="inlineStr">
         <is>
           <t>h-</t>
         </is>
       </c>
-      <c r="W70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>Causes Special Tag Throw with Michelle, see the Grappling Arts.</t>
         </is>
       </c>
-      <c r="Y70" t="inlineStr">
+      <c r="Z70" t="inlineStr">
         <is>
           <t>a2a00b1a-1750-4988-9b6c-606239b6a0c6</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
+      <c r="AA70" t="inlineStr">
         <is>
           <t>d7a8e56a-8655-4e7e-8cb3-47b5d679baf6</t>
         </is>
       </c>
-      <c r="AA70" t="inlineStr">
+      <c r="AB70" t="inlineStr">
         <is>
           <t>a72aa904-1124-409f-a75b-cb6b7a95fa1f</t>
         </is>
@@ -6531,90 +6592,95 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t>3~2</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
           <t>Tequila Sunrise</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>Tequila Sunrise</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
+      <c r="P71" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="R71" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr">
+      <c r="S71" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="T71" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W71" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>Damage is 18 on the WS+2 if followed by a string starting with 1.</t>
         </is>
       </c>
-      <c r="Y71" t="inlineStr">
+      <c r="Z71" t="inlineStr">
         <is>
           <t>50b918b4-648d-4f4f-b682-2319b146469a</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
+      <c r="AA71" t="inlineStr">
         <is>
           <t>95b94296-4b8a-4a81-a3d9-ac54f7eb3fb5</t>
         </is>
@@ -6631,87 +6697,87 @@
           <t>WS+2,2</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>– Flash Elbow</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>Tequila Sunrise – Flash Elbow</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>-20</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>-11 -20</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>0 KD</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>-6 KD</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
+      <c r="P72" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="Q72" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="R72" t="inlineStr">
         <is>
           <t>15,22</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr">
+      <c r="S72" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="T72" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="Y72" t="inlineStr">
+      <c r="Z72" t="inlineStr">
         <is>
           <t>b8c08be0-1649-4e4f-928e-d221c2f8bf81</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
+      <c r="AA72" t="inlineStr">
         <is>
           <t>97fbf846-d9a5-4bd3-adb7-98dc363d6569</t>
         </is>
       </c>
-      <c r="AA72" t="inlineStr">
+      <c r="AB72" t="inlineStr">
         <is>
           <t>50b918b4-648d-4f4f-b682-2319b146469a</t>
         </is>
@@ -6728,102 +6794,102 @@
           <t>WS+2,1,1</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>– Club Fist - Flash Uppercut</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>Tequila Sunrise – Club Fist - Flash Uppercut</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>-15 -14</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>-11 -15 -14</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t>-4 KD</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>0 -4 KD</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t>-4 KD</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
+      <c r="O73" t="inlineStr">
         <is>
           <t>-6 -4 KD</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr">
+      <c r="P73" t="inlineStr">
         <is>
           <t>5,21</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
+      <c r="Q73" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
+      <c r="R73" t="inlineStr">
         <is>
           <t>15,5,21</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr">
+      <c r="S73" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
+      <c r="T73" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="V73" t="inlineStr">
+      <c r="W73" t="inlineStr">
         <is>
           <t>SH</t>
         </is>
       </c>
-      <c r="W73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>The uppercut does not juggle, but you can buffer in a tag.</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
+      <c r="Y73" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y73" t="inlineStr">
+      <c r="Z73" t="inlineStr">
         <is>
           <t>16ae29bf-13c7-48a7-944e-bb7331713538</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
+      <c r="AA73" t="inlineStr">
         <is>
           <t>66ffb7fc-f605-44d7-b667-64994515726d</t>
         </is>
       </c>
-      <c r="AA73" t="inlineStr">
+      <c r="AB73" t="inlineStr">
         <is>
           <t>50b918b4-648d-4f4f-b682-2319b146469a</t>
         </is>
@@ -6840,87 +6906,87 @@
           <t>WS+2,1,4,3</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>– Club Fist - Bow - Arrow</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>Tequila Sunrise – Club Fist - Bow - Arrow</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>-15 -13 -12</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>-11 -15 -13 -12</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>-4 -2 KD</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>0 -4 -2 KD</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>-4 -2 KD</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>-6 -4 -2 KD</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr">
+      <c r="P74" t="inlineStr">
         <is>
           <t>5,12,15</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
+      <c r="Q74" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
+      <c r="R74" t="inlineStr">
         <is>
           <t>15,5,12,15</t>
         </is>
       </c>
-      <c r="R74" t="inlineStr">
+      <c r="S74" t="inlineStr">
         <is>
           <t>mLm</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
+      <c r="T74" t="inlineStr">
         <is>
           <t>mmLm</t>
         </is>
       </c>
-      <c r="Y74" t="inlineStr">
+      <c r="Z74" t="inlineStr">
         <is>
           <t>3308856d-d15f-45c7-8281-db3de8f037ce</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
+      <c r="AA74" t="inlineStr">
         <is>
           <t>33e320b0-7e12-4ae7-9cc4-7c606aaca590</t>
         </is>
       </c>
-      <c r="AA74" t="inlineStr">
+      <c r="AB74" t="inlineStr">
         <is>
           <t>50b918b4-648d-4f4f-b682-2319b146469a</t>
         </is>
@@ -6937,92 +7003,92 @@
           <t>WS+2,4</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>– Razor Sweep</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Tequila Sunrise – Razor Sweep</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>-11 -10</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>0 +1</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>-6 +1</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr">
+      <c r="P75" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="R75" t="inlineStr">
         <is>
           <t>15,12</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr">
+      <c r="S75" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
+      <c r="T75" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="V75" t="inlineStr">
+      <c r="W75" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Y75" t="inlineStr">
+      <c r="Z75" t="inlineStr">
         <is>
           <t>08cc0684-9307-4b9b-aa17-ec26f1a07ab2</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
+      <c r="AA75" t="inlineStr">
         <is>
           <t>6379a4b4-d174-412f-8409-cb6229426a50</t>
         </is>
       </c>
-      <c r="AA75" t="inlineStr">
+      <c r="AB75" t="inlineStr">
         <is>
           <t>50b918b4-648d-4f4f-b682-2319b146469a</t>
         </is>
@@ -7039,87 +7105,87 @@
           <t>WS+2,4,4</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>–– High Kick</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>Tequila Sunrise – Razor Sweep – High Kick</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>-19</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>-11 -10 -19</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>0 +1 -3</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
+      <c r="O76" t="inlineStr">
         <is>
           <t>-6 +1 -3</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr">
+      <c r="P76" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
+      <c r="R76" t="inlineStr">
         <is>
           <t>15,12,23</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr">
+      <c r="S76" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
+      <c r="T76" t="inlineStr">
         <is>
           <t>mLh</t>
         </is>
       </c>
-      <c r="Y76" t="inlineStr">
+      <c r="Z76" t="inlineStr">
         <is>
           <t>90abd81b-c322-4086-ac5e-1bb4b74d0f21</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
+      <c r="AA76" t="inlineStr">
         <is>
           <t>96906e1d-ecb7-4784-8c38-de478dfb34ac</t>
         </is>
       </c>
-      <c r="AA76" t="inlineStr">
+      <c r="AB76" t="inlineStr">
         <is>
           <t>08cc0684-9307-4b9b-aa17-ec26f1a07ab2</t>
         </is>
@@ -7136,92 +7202,92 @@
           <t>WS+2,4,d+4</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>–– Low Kick</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Tequila Sunrise – Razor Sweep – Low Kick</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>-11 -10 -14</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t>0 +1 -8</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
+      <c r="O77" t="inlineStr">
         <is>
           <t>-6 +1 -8</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr">
+      <c r="P77" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr">
+      <c r="R77" t="inlineStr">
         <is>
           <t>15,12,10</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr">
+      <c r="S77" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
+      <c r="T77" t="inlineStr">
         <is>
           <t>mLL</t>
         </is>
       </c>
-      <c r="V77" t="inlineStr">
+      <c r="W77" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Y77" t="inlineStr">
+      <c r="Z77" t="inlineStr">
         <is>
           <t>8780c530-485c-4854-86c9-3d8d73cf1f42</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
+      <c r="AA77" t="inlineStr">
         <is>
           <t>feea5066-7c67-4d48-8e48-c23ce014a41a</t>
         </is>
       </c>
-      <c r="AA77" t="inlineStr">
+      <c r="AB77" t="inlineStr">
         <is>
           <t>08cc0684-9307-4b9b-aa17-ec26f1a07ab2</t>
         </is>
@@ -7238,92 +7304,92 @@
           <t>WS+2,4,1</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>–– Razor's Edge</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>Tequila Sunrise – Razor Sweep – Razor's Edge</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>-18</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t>-11 -10 -18</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>0 +1 KD</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t>-6 +1 KD</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr">
+      <c r="P78" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr">
+      <c r="Q78" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr">
+      <c r="R78" t="inlineStr">
         <is>
           <t>15,12,21</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr">
+      <c r="S78" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
+      <c r="T78" t="inlineStr">
         <is>
           <t>mLm</t>
         </is>
       </c>
-      <c r="V78" t="inlineStr">
+      <c r="W78" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Y78" t="inlineStr">
+      <c r="Z78" t="inlineStr">
         <is>
           <t>d636b20f-0a5f-4b70-aea5-7122dee324e0</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
+      <c r="AA78" t="inlineStr">
         <is>
           <t>4d530135-e440-4d11-8033-58319f9a4200</t>
         </is>
       </c>
-      <c r="AA78" t="inlineStr">
+      <c r="AB78" t="inlineStr">
         <is>
           <t>08cc0684-9307-4b9b-aa17-ec26f1a07ab2</t>
         </is>
@@ -7340,92 +7406,92 @@
           <t>b+3</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>Liquid Sweep</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>Liquid Sweep</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>-33</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>-33</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
+      <c r="O79" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr">
+      <c r="P79" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
+      <c r="Q79" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr">
+      <c r="R79" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr">
+      <c r="S79" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
+      <c r="T79" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="V79" t="inlineStr">
+      <c r="W79" t="inlineStr">
         <is>
           <t>MS PLDc</t>
         </is>
       </c>
-      <c r="Y79" t="inlineStr">
+      <c r="Z79" t="inlineStr">
         <is>
           <t>081c71d9-14c8-4f81-a116-e770a0b1a68b</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
+      <c r="AA79" t="inlineStr">
         <is>
           <t>49aebb0f-7e34-49a0-a13f-9792bb666e6f</t>
         </is>
@@ -7442,87 +7508,87 @@
           <t>uf+3+4</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>Earthquale Stomp</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>Earthquale Stomp</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>-32</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>-32</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
+      <c r="O80" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr">
+      <c r="P80" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr">
+      <c r="Q80" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr">
+      <c r="R80" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr">
+      <c r="S80" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
+      <c r="T80" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="Y80" t="inlineStr">
+      <c r="Z80" t="inlineStr">
         <is>
           <t>841212ca-51a4-49fb-aa7a-fd658c5efc8f</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
+      <c r="AA80" t="inlineStr">
         <is>
           <t>04773d5e-051d-4d43-bcc6-1676ca9c396e</t>
         </is>
@@ -7539,52 +7605,52 @@
           <t>3+4</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>Counter Clockwise Spin</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>Counter Clockwise Spin</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr">
+      <c r="P81" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
+      <c r="Q81" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr">
+      <c r="R81" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr">
+      <c r="S81" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
+      <c r="T81" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W81" t="inlineStr">
+      <c r="X81" t="inlineStr">
         <is>
           <t>Chains into Spinning Razor Kick Variations. First kick will do 20 damage.</t>
         </is>
       </c>
-      <c r="Y81" t="inlineStr">
+      <c r="Z81" t="inlineStr">
         <is>
           <t>ad154462-6148-4f1a-8a02-ea05b3eeb7b2</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
+      <c r="AA81" t="inlineStr">
         <is>
           <t>778fe738-736a-40c6-bcdb-37d9cc30283f</t>
         </is>
@@ -7601,92 +7667,92 @@
           <t>d+4</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>Razor Sweep</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>Razor Sweep</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
+      <c r="O82" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr">
+      <c r="P82" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr">
+      <c r="Q82" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr">
+      <c r="R82" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr">
+      <c r="S82" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
+      <c r="T82" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="V82" t="inlineStr">
+      <c r="W82" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Y82" t="inlineStr">
+      <c r="Z82" t="inlineStr">
         <is>
           <t>3ba28285-55f5-4b5d-8de1-aec6d11f8488</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
+      <c r="AA82" t="inlineStr">
         <is>
           <t>3f71e6df-2a62-4e24-83a5-cb74227d6235</t>
         </is>
@@ -7703,87 +7769,87 @@
           <t>d+4,N+4</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>– High Kick</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>Razor Sweep – High Kick</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>-19</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t>-9 -19</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t>-10 -3</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="N83" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr">
+      <c r="O83" t="inlineStr">
         <is>
           <t>-10 -3</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr">
+      <c r="P83" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
+      <c r="Q83" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr">
+      <c r="R83" t="inlineStr">
         <is>
           <t>10,23</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr">
+      <c r="S83" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
+      <c r="T83" t="inlineStr">
         <is>
           <t>Lh</t>
         </is>
       </c>
-      <c r="Y83" t="inlineStr">
+      <c r="Z83" t="inlineStr">
         <is>
           <t>f3d36877-1a28-4c01-bab8-8229b80b79da</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
+      <c r="AA83" t="inlineStr">
         <is>
           <t>bf72a458-da43-4a73-ada1-767463f4b8b1</t>
         </is>
       </c>
-      <c r="AA83" t="inlineStr">
+      <c r="AB83" t="inlineStr">
         <is>
           <t>3ba28285-55f5-4b5d-8de1-aec6d11f8488</t>
         </is>
@@ -7800,92 +7866,92 @@
           <t>d+4,d+4</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>– Low Kick</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>Razor Sweep – Low Kick</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="K84" t="inlineStr">
         <is>
           <t>-9 -14</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t>-10 -8</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
+      <c r="N84" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
+      <c r="O84" t="inlineStr">
         <is>
           <t>-10 -8</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr">
+      <c r="P84" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr">
+      <c r="Q84" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q84" t="inlineStr">
+      <c r="R84" t="inlineStr">
         <is>
           <t>10,10</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr">
+      <c r="S84" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
+      <c r="T84" t="inlineStr">
         <is>
           <t>LL</t>
         </is>
       </c>
-      <c r="V84" t="inlineStr">
+      <c r="W84" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Y84" t="inlineStr">
+      <c r="Z84" t="inlineStr">
         <is>
           <t>cfbeee97-432b-4263-a7e2-20492b6833aa</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
+      <c r="AA84" t="inlineStr">
         <is>
           <t>47df9b3a-dfe5-48f1-8c75-b3a2a221f404</t>
         </is>
       </c>
-      <c r="AA84" t="inlineStr">
+      <c r="AB84" t="inlineStr">
         <is>
           <t>3ba28285-55f5-4b5d-8de1-aec6d11f8488</t>
         </is>
@@ -7902,92 +7968,92 @@
           <t>d+4,1</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>– Razor's Edge</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>Razor Sweep – Razor's Edge</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>-18</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t>-9 -18</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t>-10 KD</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
+      <c r="N85" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
+      <c r="O85" t="inlineStr">
         <is>
           <t>-10 KD</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr">
+      <c r="P85" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr">
+      <c r="Q85" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q85" t="inlineStr">
+      <c r="R85" t="inlineStr">
         <is>
           <t>10,21</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr">
+      <c r="S85" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr">
+      <c r="T85" t="inlineStr">
         <is>
           <t>Lm</t>
         </is>
       </c>
-      <c r="V85" t="inlineStr">
+      <c r="W85" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Y85" t="inlineStr">
+      <c r="Z85" t="inlineStr">
         <is>
           <t>4a44d096-425c-4067-a05d-ef151d6deb99</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
+      <c r="AA85" t="inlineStr">
         <is>
           <t>18c62048-2b6f-46dd-8b2e-f845a8fb9287</t>
         </is>
       </c>
-      <c r="AA85" t="inlineStr">
+      <c r="AB85" t="inlineStr">
         <is>
           <t>3ba28285-55f5-4b5d-8de1-aec6d11f8488</t>
         </is>
@@ -8004,92 +8070,92 @@
           <t>4,4</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>Spinning Razor Kicks</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>Spinning Razor Kicks</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t>-7 -7</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="K86" t="inlineStr">
         <is>
           <t>-7 -7</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t>-7 +4</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t>-7 +4</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr">
+      <c r="N86" t="inlineStr">
         <is>
           <t>KD +4</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
+      <c r="O86" t="inlineStr">
         <is>
           <t>KD +4</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr">
+      <c r="P86" t="inlineStr">
         <is>
           <t>20,12</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr">
+      <c r="Q86" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="Q86" t="inlineStr">
+      <c r="R86" t="inlineStr">
         <is>
           <t>20,12</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr">
+      <c r="S86" t="inlineStr">
         <is>
           <t>hL</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr">
+      <c r="T86" t="inlineStr">
         <is>
           <t>hL</t>
         </is>
       </c>
-      <c r="V86" t="inlineStr">
+      <c r="W86" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Y86" t="inlineStr">
+      <c r="Z86" t="inlineStr">
         <is>
           <t>cd2a0930-4241-4f8e-a1f2-8151b9814368</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
+      <c r="AA86" t="inlineStr">
         <is>
           <t>4ec9d487-7a5b-4f09-9b2e-c7316873bab2</t>
         </is>
@@ -8106,87 +8172,87 @@
           <t>4,4,4</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>– High Kick</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>Spinning Razor Kicks – High Kick</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>-19</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="K87" t="inlineStr">
         <is>
           <t>-7 -7 -19</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t>-7 +4 -3</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr">
+      <c r="N87" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr">
+      <c r="O87" t="inlineStr">
         <is>
           <t>KD +4 -3</t>
         </is>
       </c>
-      <c r="O87" t="inlineStr">
+      <c r="P87" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr">
+      <c r="Q87" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="Q87" t="inlineStr">
+      <c r="R87" t="inlineStr">
         <is>
           <t>20,12,23</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr">
+      <c r="S87" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr">
+      <c r="T87" t="inlineStr">
         <is>
           <t>hLh</t>
         </is>
       </c>
-      <c r="Y87" t="inlineStr">
+      <c r="Z87" t="inlineStr">
         <is>
           <t>a5cb7052-ba1f-4451-af2a-19be86f0f2d5</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
+      <c r="AA87" t="inlineStr">
         <is>
           <t>7b3fbc36-00ce-49a1-81c2-c3f4245c91a3</t>
         </is>
       </c>
-      <c r="AA87" t="inlineStr">
+      <c r="AB87" t="inlineStr">
         <is>
           <t>cd2a0930-4241-4f8e-a1f2-8151b9814368</t>
         </is>
@@ -8203,92 +8269,92 @@
           <t>4,4,d+4</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>– Low Kick</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>Spinning Razor Kicks – Low Kick</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="K88" t="inlineStr">
         <is>
           <t>-7 -7 -14</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
+      <c r="L88" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t>-7 +4 -8</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr">
+      <c r="N88" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr">
+      <c r="O88" t="inlineStr">
         <is>
           <t>KD +4 -8</t>
         </is>
       </c>
-      <c r="O88" t="inlineStr">
+      <c r="P88" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr">
+      <c r="Q88" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q88" t="inlineStr">
+      <c r="R88" t="inlineStr">
         <is>
           <t>20,12,10</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr">
+      <c r="S88" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="S88" t="inlineStr">
+      <c r="T88" t="inlineStr">
         <is>
           <t>hLL</t>
         </is>
       </c>
-      <c r="V88" t="inlineStr">
+      <c r="W88" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Y88" t="inlineStr">
+      <c r="Z88" t="inlineStr">
         <is>
           <t>a48608e8-1cd8-4504-8093-2ba46ddcf3b5</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
+      <c r="AA88" t="inlineStr">
         <is>
           <t>f46e6f0e-0ead-4035-927a-0da05637d7bb</t>
         </is>
       </c>
-      <c r="AA88" t="inlineStr">
+      <c r="AB88" t="inlineStr">
         <is>
           <t>cd2a0930-4241-4f8e-a1f2-8151b9814368</t>
         </is>
@@ -8305,92 +8371,92 @@
           <t>4,4,1</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>– Razor's Edge</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>Spinning Razor Kicks – Razor's Edge</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t>-18</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
+      <c r="K89" t="inlineStr">
         <is>
           <t>-7 -7 -18</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t>-7 +4 KD</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr">
+      <c r="N89" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr">
+      <c r="O89" t="inlineStr">
         <is>
           <t>KD +4 KD</t>
         </is>
       </c>
-      <c r="O89" t="inlineStr">
+      <c r="P89" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr">
+      <c r="Q89" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q89" t="inlineStr">
+      <c r="R89" t="inlineStr">
         <is>
           <t>20,12,21</t>
         </is>
       </c>
-      <c r="R89" t="inlineStr">
+      <c r="S89" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S89" t="inlineStr">
+      <c r="T89" t="inlineStr">
         <is>
           <t>hLm</t>
         </is>
       </c>
-      <c r="V89" t="inlineStr">
+      <c r="W89" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Y89" t="inlineStr">
+      <c r="Z89" t="inlineStr">
         <is>
           <t>e7b83a88-e3a4-4ac1-95df-1c49fb5c03d1</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
+      <c r="AA89" t="inlineStr">
         <is>
           <t>2b436f91-4f96-4547-adb6-fc94cf16ef56</t>
         </is>
       </c>
-      <c r="AA89" t="inlineStr">
+      <c r="AB89" t="inlineStr">
         <is>
           <t>cd2a0930-4241-4f8e-a1f2-8151b9814368</t>
         </is>
@@ -8407,92 +8473,92 @@
           <t>b+4</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>Heaven Shatter Kick</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>Heaven Shatter Kick</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
+      <c r="K90" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr">
+      <c r="N90" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr">
+      <c r="O90" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O90" t="inlineStr">
+      <c r="P90" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr">
+      <c r="Q90" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q90" t="inlineStr">
+      <c r="R90" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R90" t="inlineStr">
+      <c r="S90" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S90" t="inlineStr">
+      <c r="T90" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="V90" t="inlineStr">
+      <c r="W90" t="inlineStr">
         <is>
           <t>CSc</t>
         </is>
       </c>
-      <c r="Y90" t="inlineStr">
+      <c r="Z90" t="inlineStr">
         <is>
           <t>40a9fa54-4a0b-4476-8309-5af5eb811950</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
+      <c r="AA90" t="inlineStr">
         <is>
           <t>4fffe2cf-97b3-4e53-85f8-92cd71d03f6c</t>
         </is>
@@ -8509,92 +8575,92 @@
           <t>df+4&lt;2&lt;b,f+1</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>Mountain Crusher</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>Mountain Crusher</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>-7 -9 -15</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="K91" t="inlineStr">
         <is>
           <t>-7 -9 -15</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t>+4 -2 KD</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t>+4 -2 KD</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr">
+      <c r="N91" t="inlineStr">
         <is>
           <t>+4 -2 KD</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr">
+      <c r="O91" t="inlineStr">
         <is>
           <t>+4 -2 KD</t>
         </is>
       </c>
-      <c r="O91" t="inlineStr">
+      <c r="P91" t="inlineStr">
         <is>
           <t>12,15,25</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr">
+      <c r="Q91" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="Q91" t="inlineStr">
+      <c r="R91" t="inlineStr">
         <is>
           <t>12,15,25</t>
         </is>
       </c>
-      <c r="R91" t="inlineStr">
+      <c r="S91" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="S91" t="inlineStr">
+      <c r="T91" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="V91" t="inlineStr">
+      <c r="W91" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="Y91" t="inlineStr">
+      <c r="Z91" t="inlineStr">
         <is>
           <t>a5b44d75-f4c2-4bec-ac92-627e21532342</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
+      <c r="AA91" t="inlineStr">
         <is>
           <t>de022131-2fc1-4891-9403-47dd5f360b91</t>
         </is>
@@ -8611,87 +8677,87 @@
           <t>WS+4</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>Skyscraper Kick</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>Skyscraper Kick</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
+      <c r="K92" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr">
+      <c r="N92" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr">
+      <c r="O92" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O92" t="inlineStr">
+      <c r="P92" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr">
+      <c r="Q92" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q92" t="inlineStr">
+      <c r="R92" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R92" t="inlineStr">
+      <c r="S92" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S92" t="inlineStr">
+      <c r="T92" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y92" t="inlineStr">
+      <c r="Z92" t="inlineStr">
         <is>
           <t>7439cc3f-ce60-45de-aa27-01f58633f31e</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
+      <c r="AA92" t="inlineStr">
         <is>
           <t>80534827-d6e9-4aa2-a626-f974adc6d519</t>
         </is>
@@ -8708,87 +8774,87 @@
           <t>FC+df+4,3</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>Bow - Arrow</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>Bow - Arrow</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t>-14 -14</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="K93" t="inlineStr">
         <is>
           <t>-14 -14</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t>-3 KD</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t>-3 KD</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr">
+      <c r="N93" t="inlineStr">
         <is>
           <t>-3 KD</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr">
+      <c r="O93" t="inlineStr">
         <is>
           <t>-3 KD</t>
         </is>
       </c>
-      <c r="O93" t="inlineStr">
+      <c r="P93" t="inlineStr">
         <is>
           <t>12,15</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr">
+      <c r="Q93" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q93" t="inlineStr">
+      <c r="R93" t="inlineStr">
         <is>
           <t>12,15</t>
         </is>
       </c>
-      <c r="R93" t="inlineStr">
+      <c r="S93" t="inlineStr">
         <is>
           <t>Lm</t>
         </is>
       </c>
-      <c r="S93" t="inlineStr">
+      <c r="T93" t="inlineStr">
         <is>
           <t>Lm</t>
         </is>
       </c>
-      <c r="Y93" t="inlineStr">
+      <c r="Z93" t="inlineStr">
         <is>
           <t>f4f51a05-dcc8-4a5f-a2e8-a423c1aceae5</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
+      <c r="AA93" t="inlineStr">
         <is>
           <t>58440e18-0289-46f8-8663-32eb0a369a60</t>
         </is>
@@ -8812,45 +8878,50 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
+          <t>FC+2+4; d+1+3; d+2+4</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
           <t>Low Parry</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>Low Parry</t>
         </is>
       </c>
-      <c r="O94" t="inlineStr">
+      <c r="P94" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr">
+      <c r="Q94" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q94" t="inlineStr">
+      <c r="R94" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R94" t="inlineStr">
+      <c r="S94" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S94" t="inlineStr">
+      <c r="T94" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y94" t="inlineStr">
+      <c r="Z94" t="inlineStr">
         <is>
           <t>378397f9-a5c6-48bc-b260-44dfff87353f</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
+      <c r="AA94" t="inlineStr">
         <is>
           <t>a345769d-6667-4346-9926-12c8e2c5fa20</t>
         </is>
@@ -8867,47 +8938,47 @@
           <t>2+3+4</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>Wave Taunt</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>Wave Taunt</t>
         </is>
       </c>
-      <c r="O95" t="inlineStr">
+      <c r="P95" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P95" t="inlineStr">
+      <c r="Q95" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q95" t="inlineStr">
+      <c r="R95" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R95" t="inlineStr">
+      <c r="S95" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S95" t="inlineStr">
+      <c r="T95" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y95" t="inlineStr">
+      <c r="Z95" t="inlineStr">
         <is>
           <t>9acdca23-e347-4844-ac7f-41cf9fb1455f</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
+      <c r="AA95" t="inlineStr">
         <is>
           <t>83bfe4a8-8088-46fd-9d6a-08e13311a449</t>
         </is>
@@ -8939,125 +9010,130 @@
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E98" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E98" s="1" t="inlineStr">
+      <c r="F98" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F98" s="1" t="inlineStr">
+      <c r="G98" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G98" s="1" t="inlineStr">
+      <c r="H98" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H98" s="1" t="inlineStr">
+      <c r="I98" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I98" s="1" t="inlineStr">
+      <c r="J98" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J98" s="1" t="inlineStr">
+      <c r="K98" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K98" s="1" t="inlineStr">
+      <c r="L98" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L98" s="1" t="inlineStr">
+      <c r="M98" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M98" s="1" t="inlineStr">
+      <c r="N98" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N98" s="1" t="inlineStr">
+      <c r="O98" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O98" s="1" t="inlineStr">
+      <c r="P98" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P98" s="1" t="inlineStr">
+      <c r="Q98" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q98" s="1" t="inlineStr">
+      <c r="R98" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R98" s="1" t="inlineStr">
+      <c r="S98" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S98" s="1" t="inlineStr">
+      <c r="T98" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T98" s="1" t="inlineStr">
+      <c r="U98" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U98" s="1" t="inlineStr">
+      <c r="V98" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V98" s="1" t="inlineStr">
+      <c r="W98" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W98" s="1" t="inlineStr">
+      <c r="X98" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X98" s="1" t="inlineStr">
+      <c r="Y98" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y98" s="1" t="inlineStr">
+      <c r="Z98" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z98" s="1" t="inlineStr">
+      <c r="AA98" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA98" s="1" t="inlineStr">
+      <c r="AB98" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB98" s="1" t="inlineStr">
+      <c r="AC98" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -9074,82 +9150,82 @@
           <t>f+1+4</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>Heaven Cannon</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>Heaven Cannon</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
+      <c r="L99" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr">
+      <c r="N99" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr">
+      <c r="O99" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O99" t="inlineStr">
+      <c r="P99" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="P99" t="inlineStr">
+      <c r="Q99" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="Q99" t="inlineStr">
+      <c r="R99" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="R99" t="inlineStr">
+      <c r="S99" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="S99" t="inlineStr">
+      <c r="T99" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="V99" t="inlineStr">
+      <c r="W99" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Y99" t="inlineStr">
+      <c r="Z99" t="inlineStr">
         <is>
           <t>24a1499c-dbb1-4e04-b918-cb20db832fa6</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
+      <c r="AA99" t="inlineStr">
         <is>
           <t>b4ced4c1-763a-4eb4-b61f-c12c50bd284b</t>
         </is>
@@ -9181,125 +9257,130 @@
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E102" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E102" s="1" t="inlineStr">
+      <c r="F102" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F102" s="1" t="inlineStr">
+      <c r="G102" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G102" s="1" t="inlineStr">
+      <c r="H102" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H102" s="1" t="inlineStr">
+      <c r="I102" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I102" s="1" t="inlineStr">
+      <c r="J102" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J102" s="1" t="inlineStr">
+      <c r="K102" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K102" s="1" t="inlineStr">
+      <c r="L102" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L102" s="1" t="inlineStr">
+      <c r="M102" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M102" s="1" t="inlineStr">
+      <c r="N102" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N102" s="1" t="inlineStr">
+      <c r="O102" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O102" s="1" t="inlineStr">
+      <c r="P102" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P102" s="1" t="inlineStr">
+      <c r="Q102" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q102" s="1" t="inlineStr">
+      <c r="R102" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R102" s="1" t="inlineStr">
+      <c r="S102" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S102" s="1" t="inlineStr">
+      <c r="T102" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T102" s="1" t="inlineStr">
+      <c r="U102" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U102" s="1" t="inlineStr">
+      <c r="V102" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V102" s="1" t="inlineStr">
+      <c r="W102" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W102" s="1" t="inlineStr">
+      <c r="X102" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X102" s="1" t="inlineStr">
+      <c r="Y102" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y102" s="1" t="inlineStr">
+      <c r="Z102" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z102" s="1" t="inlineStr">
+      <c r="AA102" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA102" s="1" t="inlineStr">
+      <c r="AB102" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB102" s="1" t="inlineStr">
+      <c r="AC102" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -9316,42 +9397,42 @@
           <t>2,1,1,2,3,3,3,4,4,1</t>
         </is>
       </c>
-      <c r="O103" t="inlineStr">
+      <c r="P103" t="inlineStr">
         <is>
           <t>8,6,6,6,6,6,6,7,8,25</t>
         </is>
       </c>
-      <c r="P103" t="inlineStr">
+      <c r="Q103" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="Q103" t="inlineStr">
+      <c r="R103" t="inlineStr">
         <is>
           <t>8,6,6,6,6,6,6,7,8,25</t>
         </is>
       </c>
-      <c r="R103" t="inlineStr">
+      <c r="S103" t="inlineStr">
         <is>
           <t>hmmhLmhhLm</t>
         </is>
       </c>
-      <c r="S103" t="inlineStr">
+      <c r="T103" t="inlineStr">
         <is>
           <t>hmmhLmhhLm</t>
         </is>
       </c>
-      <c r="Y103" t="inlineStr">
+      <c r="Z103" t="inlineStr">
         <is>
           <t>f26af970-57e3-45d4-baba-6711c2809508</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
+      <c r="AA103" t="inlineStr">
         <is>
           <t>f26af970-57e3-45d4-baba-6711c2809508</t>
         </is>
       </c>
-      <c r="AB103" t="inlineStr">
+      <c r="AC103" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -9368,42 +9449,42 @@
           <t>2,1,1,2,3,3,2,3,2,1</t>
         </is>
       </c>
-      <c r="O104" t="inlineStr">
+      <c r="P104" t="inlineStr">
         <is>
           <t>8,6,6,6,6,6,7,5,5,30</t>
         </is>
       </c>
-      <c r="P104" t="inlineStr">
+      <c r="Q104" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="Q104" t="inlineStr">
+      <c r="R104" t="inlineStr">
         <is>
           <t>8,6,6,6,6,6,7,5,5,30</t>
         </is>
       </c>
-      <c r="R104" t="inlineStr">
+      <c r="S104" t="inlineStr">
         <is>
           <t>hmmhLmmLm!</t>
         </is>
       </c>
-      <c r="S104" t="inlineStr">
+      <c r="T104" t="inlineStr">
         <is>
           <t>hmmhLmmLm!</t>
         </is>
       </c>
-      <c r="Y104" t="inlineStr">
+      <c r="Z104" t="inlineStr">
         <is>
           <t>8ba99c8f-7b6d-46d5-860f-492405778df4</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
+      <c r="AA104" t="inlineStr">
         <is>
           <t>8ba99c8f-7b6d-46d5-860f-492405778df4</t>
         </is>
       </c>
-      <c r="AB104" t="inlineStr">
+      <c r="AC104" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -9420,42 +9501,42 @@
           <t>2,1,1,2,3,3,2,1,4,3</t>
         </is>
       </c>
-      <c r="O105" t="inlineStr">
+      <c r="P105" t="inlineStr">
         <is>
           <t>8,6,6,6,6,67,7,10,25</t>
         </is>
       </c>
-      <c r="P105" t="inlineStr">
+      <c r="Q105" t="inlineStr">
         <is>
           <t>141</t>
         </is>
       </c>
-      <c r="Q105" t="inlineStr">
+      <c r="R105" t="inlineStr">
         <is>
           <t>8,6,6,6,6,67,7,10,25</t>
         </is>
       </c>
-      <c r="R105" t="inlineStr">
+      <c r="S105" t="inlineStr">
         <is>
           <t>hmmhLmmmLm</t>
         </is>
       </c>
-      <c r="S105" t="inlineStr">
+      <c r="T105" t="inlineStr">
         <is>
           <t>hmmhLmmmLm</t>
         </is>
       </c>
-      <c r="Y105" t="inlineStr">
+      <c r="Z105" t="inlineStr">
         <is>
           <t>12d35c24-0209-43bc-a4fa-a6173fd493c0</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
+      <c r="AA105" t="inlineStr">
         <is>
           <t>12d35c24-0209-43bc-a4fa-a6173fd493c0</t>
         </is>
       </c>
-      <c r="AB105" t="inlineStr">
+      <c r="AC105" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
